--- a/docs/pit-tax-template-apis.xlsx
+++ b/docs/pit-tax-template-apis.xlsx
@@ -332,14 +332,14 @@
     <x:col min="9" max="9" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="15" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="15" hidden="0" customWidth="1"/>
@@ -359,8 +359,10 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>Individual Tax (PIT) Recommended Import Template</x:v>
+      <x:c r="A1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Individual Tax (PIT) Recommended Import Template</x:t>
+        </x:is>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -369,8 +371,10 @@
       <x:c r="F1" s="2"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
-        <x:v>Template: PIT_IMPORT | Version: 1.0 | Use primary provision amounts first; use User Fallback only when primary data is incomplete.</x:v>
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Template: PIT_IMPORT | Version: 1.0 | Use primary provision amounts first; use User Fallback only when primary data is incomplete.</x:t>
+        </x:is>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -379,110 +383,180 @@
       <x:c r="F2" s="2"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="6" t="str">
-        <x:v>Tax Year</x:v>
+      <x:c r="A4" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Tax Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B4" s="9" t="str">
-        <x:v>Filing Date</x:v>
+      <x:c r="B4" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Filing Date</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C4" s="6" t="str">
-        <x:v>PTIN</x:v>
+      <x:c r="C4" s="6" t="inlineStr">
+        <x:is>
+          <x:t>PTIN</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D4" s="9" t="str">
-        <x:v>Individual Name</x:v>
+      <x:c r="D4" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Individual Name</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E4" s="12" t="str">
-        <x:v>Amount #21 Overtime LAK</x:v>
+      <x:c r="E4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #21 Overtime LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F4" s="12" t="str">
-        <x:v>Amount #22 Uniform / Safety LAK</x:v>
+      <x:c r="F4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #22 Uniform / Safety LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G4" s="12" t="str">
-        <x:v>Amount #23.1 Spouse Allowance LAK</x:v>
+      <x:c r="G4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #23.1 Spouse Allowance LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H4" s="12" t="str">
-        <x:v>Amount #23.2 Child Allowance LAK</x:v>
+      <x:c r="H4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #23.2 Child Allowance LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I4" s="12" t="str">
-        <x:v>Amount #24 Government Allowance LAK</x:v>
+      <x:c r="I4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #24 Government Allowance LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J4" s="12" t="str">
-        <x:v>Amount #25 Student Allowance LAK</x:v>
+      <x:c r="J4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #25 Student Allowance LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K4" s="12" t="str">
-        <x:v>Amount #26 Share Sale Profit LAK</x:v>
+      <x:c r="K4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #26 Share Sale Profit LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L4" s="12" t="str">
-        <x:v>Lao Stock Exchange Listed?</x:v>
+      <x:c r="L4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Lao Stock Exchange Listed?</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M4" s="12" t="str">
-        <x:v>Amount #27 Dividend Income LAK</x:v>
+      <x:c r="M4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #27 Dividend Income LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="N4" s="12" t="str">
-        <x:v>Amount #28.1 Deposit Interest LAK</x:v>
+      <x:c r="N4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #28.1 Deposit Interest LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="O4" s="12" t="str">
-        <x:v>Deposit in Banking System?</x:v>
+      <x:c r="O4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Deposit in Banking System?</x:t>
+        </x:is>
       </x:c>
-      <x:c r="P4" s="12" t="str">
-        <x:v>Amount #28.2 Bond Interest LAK</x:v>
+      <x:c r="P4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #28.2 Bond Interest LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="Q4" s="12" t="str">
-        <x:v>Amount #29 Security Bonus LAK</x:v>
+      <x:c r="Q4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Amount #29 Security Bonus LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R4" s="12" t="str">
-        <x:v>Social Security Member?</x:v>
+      <x:c r="R4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Social Security Member?</x:t>
+        </x:is>
       </x:c>
-      <x:c r="S4" s="12" t="str">
-        <x:v>Social Security Contribution LAK #30</x:v>
+      <x:c r="S4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Social Security Contribution LAK #30</x:t>
+        </x:is>
       </x:c>
-      <x:c r="T4" s="15" t="str">
-        <x:v>Use User Fallback?</x:v>
+      <x:c r="T4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback?</x:t>
+        </x:is>
       </x:c>
-      <x:c r="U4" s="15" t="str">
-        <x:v>User TE #21</x:v>
+      <x:c r="U4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #21</x:t>
+        </x:is>
       </x:c>
-      <x:c r="V4" s="15" t="str">
-        <x:v>User TE #22</x:v>
+      <x:c r="V4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #22</x:t>
+        </x:is>
       </x:c>
-      <x:c r="W4" s="15" t="str">
-        <x:v>User TE #23.1</x:v>
+      <x:c r="W4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #23.1</x:t>
+        </x:is>
       </x:c>
-      <x:c r="X4" s="15" t="str">
-        <x:v>User TE #23.2</x:v>
+      <x:c r="X4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #23.2</x:t>
+        </x:is>
       </x:c>
-      <x:c r="Y4" s="15" t="str">
-        <x:v>User TE #24</x:v>
+      <x:c r="Y4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #24</x:t>
+        </x:is>
       </x:c>
-      <x:c r="Z4" s="15" t="str">
-        <x:v>User TE #25</x:v>
+      <x:c r="Z4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #25</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AA4" s="15" t="str">
-        <x:v>User TE #26</x:v>
+      <x:c r="AA4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #26</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AB4" s="15" t="str">
-        <x:v>User TE #27</x:v>
+      <x:c r="AB4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #27</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AC4" s="15" t="str">
-        <x:v>User TE #28.1</x:v>
+      <x:c r="AC4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #28.1</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AD4" s="15" t="str">
-        <x:v>User TE #28.2</x:v>
+      <x:c r="AD4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #28.2</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AE4" s="15" t="str">
-        <x:v>User TE #29</x:v>
+      <x:c r="AE4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #29</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AF4" s="15" t="str">
-        <x:v>User TE #30</x:v>
+      <x:c r="AF4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE #30</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AG4" s="15" t="str">
-        <x:v>User TE Total</x:v>
+      <x:c r="AG4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User TE Total</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AH4" s="15" t="str">
-        <x:v>User Fallback Reason</x:v>
+      <x:c r="AH4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback Reason</x:t>
+        </x:is>
       </x:c>
-      <x:c r="AI4" s="15" t="str">
-        <x:v>User Comment</x:v>
+      <x:c r="AI4" s="15" t="inlineStr">
+        <x:is>
+          <x:t>User Comment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -490,11 +564,15 @@
         <x:v>2026</x:v>
       </x:c>
       <x:c r="B5" s="23"/>
-      <x:c r="C5" s="24" t="str">
-        <x:v>12345678</x:v>
+      <x:c r="C5" s="24" t="inlineStr">
+        <x:is>
+          <x:t>12345678</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D5" s="24" t="str">
-        <x:v>Example Individual</x:v>
+      <x:c r="D5" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Example Individual</x:t>
+        </x:is>
       </x:c>
       <x:c r="E5" s="25" t="n">
         <x:v>20000000</x:v>
@@ -517,8 +595,10 @@
       <x:c r="K5" s="25" t="n">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="L5" s="24" t="str">
-        <x:v>Yes</x:v>
+      <x:c r="L5" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
       </x:c>
       <x:c r="M5" s="25" t="n">
         <x:v>0</x:v>
@@ -526,8 +606,10 @@
       <x:c r="N5" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O5" s="24" t="str">
-        <x:v>No</x:v>
+      <x:c r="O5" s="24" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
       </x:c>
       <x:c r="P5" s="25" t="n">
         <x:v>0</x:v>
@@ -535,14 +617,18 @@
       <x:c r="Q5" s="25" t="n">
         <x:v>25000000</x:v>
       </x:c>
-      <x:c r="R5" s="24" t="str">
-        <x:v>No</x:v>
+      <x:c r="R5" s="24" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
       </x:c>
       <x:c r="S5" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="T5" s="24" t="str">
-        <x:v>No</x:v>
+      <x:c r="T5" s="24" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
       </x:c>
       <x:c r="U5" s="25"/>
       <x:c r="V5" s="25"/>
@@ -557,8 +643,8 @@
       <x:c r="AE5" s="25"/>
       <x:c r="AF5" s="25"/>
       <x:c r="AG5" s="25"/>
-      <x:c r="AH5" s="24" t="str"/>
-      <x:c r="AI5" s="24" t="str"/>
+      <x:c r="AH5" s="24"/>
+      <x:c r="AI5" s="24"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="18"/>
@@ -37528,7 +37614,6 @@
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:dataValidations count="4">
     <x:dataValidation type="whole" operator="between" allowBlank="0" showErrorMessage="1" sqref="A5:A1004">
       <x:formula1>2000</x:formula1>
@@ -37544,6 +37629,7 @@
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -37558,221 +37644,321 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>PIT Import Template - Instructions</x:v>
+      <x:c r="A1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>PIT Import Template - Instructions</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="30" t="str">
-        <x:v>Information Type</x:v>
+      <x:c r="A3" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Information Type</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="str">
-        <x:v>Color</x:v>
+      <x:c r="B3" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Color</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C3" s="30" t="str">
-        <x:v>Meaning</x:v>
+      <x:c r="C3" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Meaning</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D3" s="30" t="str">
-        <x:v>Examples</x:v>
+      <x:c r="D3" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Examples</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
-        <x:v>Primary Required</x:v>
+      <x:c r="A4" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Primary Required</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>Dark blue header, light blue input cells</x:v>
+      <x:c r="B4" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue header, light blue input cells</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C4" s="8" t="str">
-        <x:v>Must be completed for every PIT import row.</x:v>
+      <x:c r="C4" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Must be completed for every PIT import row.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D4" s="8" t="str">
-        <x:v>Tax Year, PTIN</x:v>
+      <x:c r="D4" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Tax Year, PTIN</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
-        <x:v>Primary Conditional</x:v>
+      <x:c r="A5" s="14" t="inlineStr">
+        <x:is>
+          <x:t>Primary Conditional</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>Medium blue header, near-white input cells</x:v>
+      <x:c r="B5" s="14" t="inlineStr">
+        <x:is>
+          <x:t>Medium blue header, near-white input cells</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>Complete only when the related PIT provision applies.</x:v>
+      <x:c r="C5" s="14" t="inlineStr">
+        <x:is>
+          <x:t>Complete only when the related PIT provision applies.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>Provision amounts #21-#30, stock exchange flag, bank deposit flag, social security fields</x:v>
+      <x:c r="D5" s="14" t="inlineStr">
+        <x:is>
+          <x:t>Provision amounts #21-#30, stock exchange flag, bank deposit flag, social security fields</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
-        <x:v>Primary Optional</x:v>
+      <x:c r="A6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>Primary Optional</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>Slate/gray-blue header, white input cells</x:v>
+      <x:c r="B6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>Slate/gray-blue header, white input cells</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>Helpful for review but not always required for calculation.</x:v>
+      <x:c r="C6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>Helpful for review but not always required for calculation.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>Filing Date, Individual Name</x:v>
+      <x:c r="D6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>Filing Date, Individual Name</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="17" t="str">
-        <x:v>User Fallback</x:v>
+      <x:c r="A7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B7" s="17" t="str">
-        <x:v>Orange header, light amber input cells</x:v>
+      <x:c r="B7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Orange header, light amber input cells</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C7" s="17" t="str">
-        <x:v>Optional user-provided TE values used only when primary information is incomplete or special judgement is required.</x:v>
+      <x:c r="C7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Optional user-provided TE values used only when primary information is incomplete or special judgement is required.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D7" s="17" t="str">
-        <x:v>Use User Fallback?, User TE #21-#30, User TE Total, User Fallback Reason</x:v>
+      <x:c r="D7" s="17" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback?, User TE #21-#30, User TE Total, User Fallback Reason</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="28" t="str">
-        <x:v>Protected Reference Sheets</x:v>
+      <x:c r="A8" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Protected Reference Sheets</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B8" s="28" t="str">
-        <x:v>Dark blue headers</x:v>
+      <x:c r="B8" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue headers</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C8" s="28" t="str">
-        <x:v>Instructions, Validation Lists, and Data Dictionary are read-only to avoid accidental changes.</x:v>
+      <x:c r="C8" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Instructions, Validation Lists, and Data Dictionary are read-only to avoid accidental changes.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D8" s="28" t="str">
-        <x:v>Use PIT Import for data entry.</x:v>
+      <x:c r="D8" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Use PIT Import for data entry.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="28" t="str"/>
-      <x:c r="B9" s="28" t="str"/>
-      <x:c r="C9" s="28" t="str"/>
-      <x:c r="D9" s="28" t="str"/>
+      <x:c r="A9" s="28"/>
+      <x:c r="B9" s="28"/>
+      <x:c r="C9" s="28"/>
+      <x:c r="D9" s="28"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="30" t="str">
-        <x:v>Rule</x:v>
+      <x:c r="A10" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Rule</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B10" s="30" t="str">
-        <x:v>Description</x:v>
+      <x:c r="B10" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C10" s="30" t="str"/>
-      <x:c r="D10" s="30" t="str"/>
+      <x:c r="C10" s="30"/>
+      <x:c r="D10" s="30"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="28" t="str">
-        <x:v>Use first sheet only</x:v>
+      <x:c r="A11" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Use first sheet only</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B11" s="28" t="str">
-        <x:v>Users should enter data in PIT Import only. Other sheets are instructions and references.</x:v>
+      <x:c r="B11" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Users should enter data in PIT Import only. Other sheets are instructions and references.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C11" s="28" t="str"/>
-      <x:c r="D11" s="28" t="str"/>
+      <x:c r="C11" s="28"/>
+      <x:c r="D11" s="28"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="28" t="str">
-        <x:v>Use primary first</x:v>
+      <x:c r="A12" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Use primary first</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B12" s="28" t="str">
-        <x:v>Enter raw income or allowance amounts by PIT provision. The system should calculate benchmark and TE from those amounts when possible.</x:v>
+      <x:c r="B12" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Enter raw income or allowance amounts by PIT provision. The system should calculate benchmark and TE from those amounts when possible.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C12" s="28" t="str"/>
-      <x:c r="D12" s="28" t="str"/>
+      <x:c r="C12" s="28"/>
+      <x:c r="D12" s="28"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="28" t="str">
-        <x:v>No simple Excel calculations</x:v>
+      <x:c r="A13" s="28" t="inlineStr">
+        <x:is>
+          <x:t>No simple Excel calculations</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B13" s="28" t="str">
-        <x:v>Do not add calculated TE columns that multiply amount by rate. The system should handle that logic.</x:v>
+      <x:c r="B13" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Do not add calculated TE columns that multiply amount by rate. The system should handle that logic.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C13" s="28" t="str"/>
-      <x:c r="D13" s="28" t="str"/>
+      <x:c r="C13" s="28"/>
+      <x:c r="D13" s="28"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="28" t="str">
-        <x:v>Fallback rule</x:v>
+      <x:c r="A14" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Fallback rule</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B14" s="28" t="str">
-        <x:v>Use User Fallback only when normal primary data is incomplete or a special user judgement is required.</x:v>
+      <x:c r="B14" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback only when normal primary data is incomplete or a special user judgement is required.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C14" s="28" t="str"/>
-      <x:c r="D14" s="28" t="str"/>
+      <x:c r="C14" s="28"/>
+      <x:c r="D14" s="28"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="28" t="str">
-        <x:v>Fallback reason</x:v>
+      <x:c r="A15" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Fallback reason</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B15" s="28" t="str">
-        <x:v>Required when Use User Fallback? is Yes.</x:v>
+      <x:c r="B15" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Required when Use User Fallback? is Yes.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C15" s="28" t="str"/>
-      <x:c r="D15" s="28" t="str"/>
+      <x:c r="C15" s="28"/>
+      <x:c r="D15" s="28"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="28" t="str">
-        <x:v>Yes/No fields</x:v>
+      <x:c r="A16" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Yes/No fields</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B16" s="28" t="str">
-        <x:v>Select Yes or No from dropdowns for stock exchange, banking system, social security, and fallback usage.</x:v>
+      <x:c r="B16" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Select Yes or No from dropdowns for stock exchange, banking system, social security, and fallback usage.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C16" s="28" t="str"/>
-      <x:c r="D16" s="28" t="str"/>
+      <x:c r="C16" s="28"/>
+      <x:c r="D16" s="28"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="28" t="str">
-        <x:v>Mandatory fields</x:v>
+      <x:c r="A17" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Mandatory fields</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B17" s="28" t="str">
-        <x:v>Tax Year and PTIN are required. At least one PIT provision amount or user fallback TE should be entered for a useful row.</x:v>
+      <x:c r="B17" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Tax Year and PTIN are required. At least one PIT provision amount or user fallback TE should be entered for a useful row.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C17" s="28" t="str"/>
-      <x:c r="D17" s="28" t="str"/>
+      <x:c r="C17" s="28"/>
+      <x:c r="D17" s="28"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="28" t="str">
-        <x:v>Expert file comparison</x:v>
+      <x:c r="A18" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Expert file comparison</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B18" s="28" t="str">
-        <x:v>The first expert workbook included calculated TE columns and summary columns. The second expert workbook removed those fields. This APIS template keeps that simpler direction while adding controlled fallback fields.</x:v>
+      <x:c r="B18" s="28" t="inlineStr">
+        <x:is>
+          <x:t>The first expert workbook included calculated TE columns and summary columns. The second expert workbook removed those fields. This APIS template keeps that simpler direction while adding controlled fallback fields.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C18" s="28" t="str"/>
-      <x:c r="D18" s="28" t="str"/>
+      <x:c r="C18" s="28"/>
+      <x:c r="D18" s="28"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="28" t="str">
-        <x:v>Template version</x:v>
+      <x:c r="A19" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Template version</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B19" s="28" t="str">
-        <x:v>PIT_IMPORT v1.0</x:v>
+      <x:c r="B19" s="28" t="inlineStr">
+        <x:is>
+          <x:t>PIT_IMPORT v1.0</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C19" s="28" t="str"/>
-      <x:c r="D19" s="28" t="str"/>
+      <x:c r="C19" s="28"/>
+      <x:c r="D19" s="28"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="28" t="str">
-        <x:v>Protection password</x:v>
+      <x:c r="A20" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Protection password</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B20" s="28" t="str">
-        <x:v>TaxETS2026</x:v>
+      <x:c r="B20" s="28" t="inlineStr">
+        <x:is>
+          <x:t>TaxETS2026</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C20" s="28" t="str">
-        <x:v>Used only to prevent accidental edits to read-only sheets.</x:v>
+      <x:c r="C20" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Used only to prevent accidental edits to read-only sheets.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D20" s="28" t="str"/>
+      <x:c r="D20" s="28"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="28" t="str">
-        <x:v>Import code note</x:v>
+      <x:c r="A21" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Import code note</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B21" s="28" t="str">
-        <x:v>Current PHP import still maps the old A:AC layout. After agreement, import_individual.php should be updated to read this final PIT_IMPORT layout by header name.</x:v>
+      <x:c r="B21" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Current PHP import still maps the old A:AC layout. After agreement, import_individual.php should be updated to read this final PIT_IMPORT layout by header name.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C21" s="28" t="str"/>
-      <x:c r="D21" s="28" t="str"/>
+      <x:c r="C21" s="28"/>
+      <x:c r="D21" s="28"/>
     </x:row>
   </x:sheetData>
   <x:sheetProtection password="C3BC" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -37792,299 +37978,475 @@
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="57.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="57.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="32.5" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="32.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="27" t="str">
-        <x:v>Yes/No</x:v>
+      <x:c r="A1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Yes/No</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B1" s="27" t="str"/>
-      <x:c r="C1" s="27" t="str">
-        <x:v>Fallback Reason</x:v>
+      <x:c r="B1" s="27"/>
+      <x:c r="C1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Fallback Reason</x:t>
+        </x:is>
       </x:c>
       <x:c r="D1" s="27"/>
-      <x:c r="E1" s="27" t="str">
-        <x:v>Provision</x:v>
+      <x:c r="E1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Provision</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F1" s="27" t="str">
-        <x:v>Legal Basis</x:v>
+      <x:c r="F1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Legal Basis</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G1" s="27" t="str">
-        <x:v>Type</x:v>
+      <x:c r="G1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Type</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H1" s="27" t="str">
-        <x:v>Description</x:v>
+      <x:c r="H1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I1" s="27" t="str">
-        <x:v>Purpose</x:v>
+      <x:c r="I1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Purpose</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J1" s="27" t="str">
-        <x:v>Primary Field</x:v>
+      <x:c r="J1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Primary Field</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K1" s="27" t="str">
-        <x:v>Fallback Field</x:v>
+      <x:c r="K1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Fallback Field</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>No</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C2" t="str"/>
-      <x:c r="E2" t="str">
-        <x:v>21</x:v>
+      <x:c r="C2"/>
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t>21</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F2" t="str">
-        <x:v>ITL., Art. 35.3</x:v>
+      <x:c r="F2" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art. 35.3</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G2" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G2" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H2" t="str">
-        <x:v>Overtime payments for employees receiving basic salary &lt;= 2M LAK</x:v>
+      <x:c r="H2" t="inlineStr">
+        <x:is>
+          <x:t>Overtime payments for employees receiving basic salary &lt;= 2M LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I2" t="str">
-        <x:v>Social</x:v>
+      <x:c r="I2" t="inlineStr">
+        <x:is>
+          <x:t>Social</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J2" t="str">
-        <x:v>Amount #21 Overtime LAK</x:v>
+      <x:c r="J2" t="inlineStr">
+        <x:is>
+          <x:t>Amount #21 Overtime LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K2" t="str">
-        <x:v>User TE #21</x:v>
+      <x:c r="K2" t="inlineStr">
+        <x:is>
+          <x:t>User TE #21</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>Yes</x:v>
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Missing tax paid data</x:v>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t>Missing tax paid data</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E3" t="str">
-        <x:v>22</x:v>
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t>22</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F3" t="str">
-        <x:v>ITL., Art. 35.20</x:v>
+      <x:c r="F3" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art. 35.20</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G3" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G3" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H3" t="str">
-        <x:v>Uniforms and equipment for preventing labour accidents</x:v>
+      <x:c r="H3" t="inlineStr">
+        <x:is>
+          <x:t>Uniforms and equipment for preventing labour accidents</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I3" t="str">
-        <x:v>Social / Health</x:v>
+      <x:c r="I3" t="inlineStr">
+        <x:is>
+          <x:t>Social / Health</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J3" t="str">
-        <x:v>Amount #22 Uniform / Safety LAK</x:v>
+      <x:c r="J3" t="inlineStr">
+        <x:is>
+          <x:t>Amount #22 Uniform / Safety LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K3" t="str">
-        <x:v>User TE #22</x:v>
+      <x:c r="K3" t="inlineStr">
+        <x:is>
+          <x:t>User TE #22</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="C4" t="str">
-        <x:v>Missing taxable base detail</x:v>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t>Missing taxable base detail</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E4" t="str">
-        <x:v>23</x:v>
+      <x:c r="E4" t="inlineStr">
+        <x:is>
+          <x:t>23</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F4" t="str">
-        <x:v>ITL., Art.35.3</x:v>
+      <x:c r="F4" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.3</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G4" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G4" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H4" t="str">
-        <x:v>Personal allowance for spouse/children (max 15M/year)</x:v>
+      <x:c r="H4" t="inlineStr">
+        <x:is>
+          <x:t>Personal allowance for spouse/children (max 15M/year)</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I4" t="str">
-        <x:v>Social</x:v>
+      <x:c r="I4" t="inlineStr">
+        <x:is>
+          <x:t>Social</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J4" t="str">
-        <x:v>Amount #23.1 / #23.2 Allowances LAK</x:v>
+      <x:c r="J4" t="inlineStr">
+        <x:is>
+          <x:t>Amount #23.1 / #23.2 Allowances LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K4" t="str">
-        <x:v>User TE #23.1 / #23.2</x:v>
+      <x:c r="K4" t="inlineStr">
+        <x:is>
+          <x:t>User TE #23.1 / #23.2</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="C5" t="str">
-        <x:v>Special legal treatment</x:v>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t>Special legal treatment</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E5" t="str">
-        <x:v>24</x:v>
+      <x:c r="E5" t="inlineStr">
+        <x:is>
+          <x:t>24</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F5" t="str">
-        <x:v>ITL., Art.35.3</x:v>
+      <x:c r="F5" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.3</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G5" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G5" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H5" t="str">
-        <x:v>Government and National Assembly personnel allowances</x:v>
+      <x:c r="H5" t="inlineStr">
+        <x:is>
+          <x:t>Government and National Assembly personnel allowances</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I5" t="str">
-        <x:v>Social</x:v>
+      <x:c r="I5" t="inlineStr">
+        <x:is>
+          <x:t>Social</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J5" t="str">
-        <x:v>Amount #24 Government Allowance LAK</x:v>
+      <x:c r="J5" t="inlineStr">
+        <x:is>
+          <x:t>Amount #24 Government Allowance LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K5" t="str">
-        <x:v>User TE #24</x:v>
+      <x:c r="K5" t="inlineStr">
+        <x:is>
+          <x:t>User TE #24</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="C6" t="str">
-        <x:v>Legacy assessment</x:v>
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t>Legacy assessment</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E6" t="str">
-        <x:v>25</x:v>
+      <x:c r="E6" t="inlineStr">
+        <x:is>
+          <x:t>25</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F6" t="str">
-        <x:v>ITL., Art.35.3</x:v>
+      <x:c r="F6" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.3</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G6" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G6" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H6" t="str">
-        <x:v>Allowances for students</x:v>
+      <x:c r="H6" t="inlineStr">
+        <x:is>
+          <x:t>Allowances for students</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I6" t="str">
-        <x:v>Social</x:v>
+      <x:c r="I6" t="inlineStr">
+        <x:is>
+          <x:t>Social</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J6" t="str">
-        <x:v>Amount #25 Student Allowance LAK</x:v>
+      <x:c r="J6" t="inlineStr">
+        <x:is>
+          <x:t>Amount #25 Student Allowance LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K6" t="str">
-        <x:v>User TE #25</x:v>
+      <x:c r="K6" t="inlineStr">
+        <x:is>
+          <x:t>User TE #25</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="C7" t="str">
-        <x:v>Manual expert review</x:v>
+      <x:c r="C7" t="inlineStr">
+        <x:is>
+          <x:t>Manual expert review</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E7" t="str">
-        <x:v>26</x:v>
+      <x:c r="E7" t="inlineStr">
+        <x:is>
+          <x:t>26</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F7" t="str">
-        <x:v>ITL., Art.35.4</x:v>
+      <x:c r="F7" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.4</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G7" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G7" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H7" t="str">
-        <x:v>Profits from sale of shares on Lao stock exchange</x:v>
+      <x:c r="H7" t="inlineStr">
+        <x:is>
+          <x:t>Profits from sale of shares on Lao stock exchange</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I7" t="str">
-        <x:v>Financial Sector</x:v>
+      <x:c r="I7" t="inlineStr">
+        <x:is>
+          <x:t>Financial Sector</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J7" t="str">
-        <x:v>Amount #26 Share Sale Profit LAK</x:v>
+      <x:c r="J7" t="inlineStr">
+        <x:is>
+          <x:t>Amount #26 Share Sale Profit LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K7" t="str">
-        <x:v>User TE #26</x:v>
+      <x:c r="K7" t="inlineStr">
+        <x:is>
+          <x:t>User TE #26</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="C8" t="str">
-        <x:v>User judgment</x:v>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t>User judgment</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E8" t="str">
-        <x:v>27</x:v>
+      <x:c r="E8" t="inlineStr">
+        <x:is>
+          <x:t>27</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F8" t="str">
-        <x:v>ITL., Art.35.4</x:v>
+      <x:c r="F8" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.4</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G8" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G8" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H8" t="str">
-        <x:v>Dividends from stock exchange registered companies</x:v>
+      <x:c r="H8" t="inlineStr">
+        <x:is>
+          <x:t>Dividends from stock exchange registered companies</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I8" t="str">
-        <x:v>Financial Sector</x:v>
+      <x:c r="I8" t="inlineStr">
+        <x:is>
+          <x:t>Financial Sector</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J8" t="str">
-        <x:v>Amount #27 Dividend Income LAK</x:v>
+      <x:c r="J8" t="inlineStr">
+        <x:is>
+          <x:t>Amount #27 Dividend Income LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K8" t="str">
-        <x:v>User TE #27</x:v>
+      <x:c r="K8" t="inlineStr">
+        <x:is>
+          <x:t>User TE #27</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="C9" t="str">
-        <x:v>Other</x:v>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>Other</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E9" t="str">
-        <x:v>28</x:v>
+      <x:c r="E9" t="inlineStr">
+        <x:is>
+          <x:t>28</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F9" t="str">
-        <x:v>ITL., Art.35.11</x:v>
+      <x:c r="F9" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.11</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G9" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G9" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H9" t="str">
-        <x:v>Interest on bank deposits and government bonds</x:v>
+      <x:c r="H9" t="inlineStr">
+        <x:is>
+          <x:t>Interest on bank deposits and government bonds</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I9" t="str">
-        <x:v>Encourage Savings</x:v>
+      <x:c r="I9" t="inlineStr">
+        <x:is>
+          <x:t>Encourage Savings</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J9" t="str">
-        <x:v>Amount #28.1 / #28.2 Interest LAK</x:v>
+      <x:c r="J9" t="inlineStr">
+        <x:is>
+          <x:t>Amount #28.1 / #28.2 Interest LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K9" t="str">
-        <x:v>User TE #28.1 / #28.2</x:v>
+      <x:c r="K9" t="inlineStr">
+        <x:is>
+          <x:t>User TE #28.1 / #28.2</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="E10" t="str">
-        <x:v>29</x:v>
+      <x:c r="E10" t="inlineStr">
+        <x:is>
+          <x:t>29</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F10" t="str">
-        <x:v>ITL., Art.35.13</x:v>
+      <x:c r="F10" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.13</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G10" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="G10" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H10" t="str">
-        <x:v>Performance bonus for security monitoring/preventing illegal acts</x:v>
+      <x:c r="H10" t="inlineStr">
+        <x:is>
+          <x:t>Performance bonus for security monitoring/preventing illegal acts</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I10" t="str">
-        <x:v>National Security</x:v>
+      <x:c r="I10" t="inlineStr">
+        <x:is>
+          <x:t>National Security</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J10" t="str">
-        <x:v>Amount #29 Security Bonus LAK</x:v>
+      <x:c r="J10" t="inlineStr">
+        <x:is>
+          <x:t>Amount #29 Security Bonus LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K10" t="str">
-        <x:v>User TE #29</x:v>
+      <x:c r="K10" t="inlineStr">
+        <x:is>
+          <x:t>User TE #29</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="E11" t="str">
-        <x:v>30</x:v>
+      <x:c r="E11" t="inlineStr">
+        <x:is>
+          <x:t>30</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F11" t="str">
-        <x:v>Notice 0824/LSO</x:v>
+      <x:c r="F11" t="inlineStr">
+        <x:is>
+          <x:t>Notice 0824/LSO</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G11" t="str">
-        <x:v>Deduction</x:v>
+      <x:c r="G11" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H11" t="str">
-        <x:v>Social security contributions (5.5%, max base 4.5M/mo)</x:v>
+      <x:c r="H11" t="inlineStr">
+        <x:is>
+          <x:t>Social security contributions (5.5%, max base 4.5M/mo)</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I11" t="str">
-        <x:v>Encourage Savings</x:v>
+      <x:c r="I11" t="inlineStr">
+        <x:is>
+          <x:t>Encourage Savings</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J11" t="str">
-        <x:v>Social Security Contribution LAK #30</x:v>
+      <x:c r="J11" t="inlineStr">
+        <x:is>
+          <x:t>Social Security Contribution LAK #30</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K11" t="str">
-        <x:v>User TE #30</x:v>
+      <x:c r="K11" t="inlineStr">
+        <x:is>
+          <x:t>User TE #30</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -38100,94 +38462,140 @@
     <x:col min="1" max="1" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="57.5" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="31.25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="31.25" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="31.25" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="16.25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="57.5" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="31.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="31.25" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="31.25" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18.75" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>PIT Provision</x:v>
+      <x:c r="A1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>PIT Provision</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>Legal Basis</x:v>
+      <x:c r="B1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Legal Basis</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>Type</x:v>
+      <x:c r="C1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Type</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>Description</x:v>
+      <x:c r="D1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>Purpose</x:v>
+      <x:c r="E1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Purpose</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>Primary Amount Field</x:v>
+      <x:c r="F1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Primary Amount Field</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G1" s="2" t="str">
-        <x:v>User Fallback Field</x:v>
+      <x:c r="G1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback Field</x:t>
+        </x:is>
       </x:c>
       <x:c r="H1" s="2"/>
-      <x:c r="I1" s="2" t="str">
-        <x:v>Start Year</x:v>
+      <x:c r="I1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Start Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J1" s="2" t="str">
-        <x:v>End Year</x:v>
+      <x:c r="J1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>End Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K1" s="2" t="str">
-        <x:v>Min Income</x:v>
+      <x:c r="K1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Min Income</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L1" s="2" t="str">
-        <x:v>Max Income</x:v>
+      <x:c r="L1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Max Income</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M1" s="2" t="str">
-        <x:v>Rate %</x:v>
+      <x:c r="M1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Rate %</x:t>
+        </x:is>
       </x:c>
       <x:c r="N1" s="2"/>
-      <x:c r="O1" s="2" t="str">
-        <x:v>Start Year</x:v>
+      <x:c r="O1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Start Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="P1" s="2" t="str">
-        <x:v>End Year</x:v>
+      <x:c r="P1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>End Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="Q1" s="2" t="str">
-        <x:v>Income Type</x:v>
+      <x:c r="Q1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Income Type</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R1" s="2" t="str">
-        <x:v>Rate %</x:v>
+      <x:c r="R1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>Rate %</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>21</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t>21</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B2" t="str">
-        <x:v>ITL., Art. 35.3</x:v>
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art. 35.3</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D2" t="str">
-        <x:v>Overtime payments for employees receiving basic salary &lt;= 2M LAK</x:v>
+      <x:c r="D2" t="inlineStr">
+        <x:is>
+          <x:t>Overtime payments for employees receiving basic salary &lt;= 2M LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E2" t="str">
-        <x:v>Social</x:v>
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t>Social</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F2" t="str">
-        <x:v>Amount #21 Overtime LAK</x:v>
+      <x:c r="F2" t="inlineStr">
+        <x:is>
+          <x:t>Amount #21 Overtime LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G2" t="str">
-        <x:v>User TE #21</x:v>
+      <x:c r="G2" t="inlineStr">
+        <x:is>
+          <x:t>User TE #21</x:t>
+        </x:is>
       </x:c>
       <x:c r="I2" t="n">
         <x:v>2020</x:v>
@@ -38195,14 +38603,20 @@
       <x:c r="J2" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="K2" t="str">
-        <x:v>0.00</x:v>
+      <x:c r="K2" t="inlineStr">
+        <x:is>
+          <x:t>0.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L2" t="str">
-        <x:v>1300000.00</x:v>
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>1300000.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M2" t="str">
-        <x:v>0.00</x:v>
+      <x:c r="M2" t="inlineStr">
+        <x:is>
+          <x:t>0.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="O2" t="n">
         <x:v>2020</x:v>
@@ -38210,34 +38624,52 @@
       <x:c r="P2" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q2" t="str">
-        <x:v>Consulting Fees</x:v>
+      <x:c r="Q2" t="inlineStr">
+        <x:is>
+          <x:t>Consulting Fees</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R2" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="R2" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>22</x:v>
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t>22</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B3" t="str">
-        <x:v>ITL., Art. 35.20</x:v>
+      <x:c r="B3" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art. 35.20</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D3" t="str">
-        <x:v>Uniforms and equipment for preventing labour accidents</x:v>
+      <x:c r="D3" t="inlineStr">
+        <x:is>
+          <x:t>Uniforms and equipment for preventing labour accidents</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E3" t="str">
-        <x:v>Social / Health</x:v>
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t>Social / Health</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F3" t="str">
-        <x:v>Amount #22 Uniform / Safety LAK</x:v>
+      <x:c r="F3" t="inlineStr">
+        <x:is>
+          <x:t>Amount #22 Uniform / Safety LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G3" t="str">
-        <x:v>User TE #22</x:v>
+      <x:c r="G3" t="inlineStr">
+        <x:is>
+          <x:t>User TE #22</x:t>
+        </x:is>
       </x:c>
       <x:c r="I3" t="n">
         <x:v>2020</x:v>
@@ -38245,14 +38677,20 @@
       <x:c r="J3" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="K3" t="str">
-        <x:v>1300001.00</x:v>
+      <x:c r="K3" t="inlineStr">
+        <x:is>
+          <x:t>1300001.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L3" t="str">
-        <x:v>5000000.00</x:v>
+      <x:c r="L3" t="inlineStr">
+        <x:is>
+          <x:t>5000000.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M3" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="M3" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="O3" t="n">
         <x:v>2020</x:v>
@@ -38260,34 +38698,52 @@
       <x:c r="P3" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q3" t="str">
-        <x:v>Dividends</x:v>
+      <x:c r="Q3" t="inlineStr">
+        <x:is>
+          <x:t>Dividends</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R3" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="R3" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>23</x:v>
+      <x:c r="A4" t="inlineStr">
+        <x:is>
+          <x:t>23</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B4" t="str">
-        <x:v>ITL., Art.35.3</x:v>
+      <x:c r="B4" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.3</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D4" t="str">
-        <x:v>Personal allowance for spouse/children (max 15M/year)</x:v>
+      <x:c r="D4" t="inlineStr">
+        <x:is>
+          <x:t>Personal allowance for spouse/children (max 15M/year)</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E4" t="str">
-        <x:v>Social</x:v>
+      <x:c r="E4" t="inlineStr">
+        <x:is>
+          <x:t>Social</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F4" t="str">
-        <x:v>Amount #23.1 / #23.2 Allowances LAK</x:v>
+      <x:c r="F4" t="inlineStr">
+        <x:is>
+          <x:t>Amount #23.1 / #23.2 Allowances LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G4" t="str">
-        <x:v>User TE #23.1 / #23.2</x:v>
+      <x:c r="G4" t="inlineStr">
+        <x:is>
+          <x:t>User TE #23.1 / #23.2</x:t>
+        </x:is>
       </x:c>
       <x:c r="I4" t="n">
         <x:v>2020</x:v>
@@ -38295,14 +38751,20 @@
       <x:c r="J4" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="K4" t="str">
-        <x:v>5000001.00</x:v>
+      <x:c r="K4" t="inlineStr">
+        <x:is>
+          <x:t>5000001.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L4" t="str">
-        <x:v>15000000.00</x:v>
+      <x:c r="L4" t="inlineStr">
+        <x:is>
+          <x:t>15000000.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M4" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="M4" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="O4" t="n">
         <x:v>2020</x:v>
@@ -38310,34 +38772,52 @@
       <x:c r="P4" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q4" t="str">
-        <x:v>Gifts (cash/kind)</x:v>
+      <x:c r="Q4" t="inlineStr">
+        <x:is>
+          <x:t>Gifts (cash/kind)</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R4" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="R4" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>24</x:v>
+      <x:c r="A5" t="inlineStr">
+        <x:is>
+          <x:t>24</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>ITL., Art.35.3</x:v>
+      <x:c r="B5" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.3</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D5" t="str">
-        <x:v>Government and National Assembly personnel allowances</x:v>
+      <x:c r="D5" t="inlineStr">
+        <x:is>
+          <x:t>Government and National Assembly personnel allowances</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E5" t="str">
-        <x:v>Social</x:v>
+      <x:c r="E5" t="inlineStr">
+        <x:is>
+          <x:t>Social</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F5" t="str">
-        <x:v>Amount #24 Government Allowance LAK</x:v>
+      <x:c r="F5" t="inlineStr">
+        <x:is>
+          <x:t>Amount #24 Government Allowance LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G5" t="str">
-        <x:v>User TE #24</x:v>
+      <x:c r="G5" t="inlineStr">
+        <x:is>
+          <x:t>User TE #24</x:t>
+        </x:is>
       </x:c>
       <x:c r="I5" t="n">
         <x:v>2020</x:v>
@@ -38345,14 +38825,20 @@
       <x:c r="J5" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="K5" t="str">
-        <x:v>15000001.00</x:v>
+      <x:c r="K5" t="inlineStr">
+        <x:is>
+          <x:t>15000001.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L5" t="str">
-        <x:v>25000000.00</x:v>
+      <x:c r="L5" t="inlineStr">
+        <x:is>
+          <x:t>25000000.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M5" t="str">
-        <x:v>15.00</x:v>
+      <x:c r="M5" t="inlineStr">
+        <x:is>
+          <x:t>15.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="O5" t="n">
         <x:v>2020</x:v>
@@ -38360,34 +38846,52 @@
       <x:c r="P5" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q5" t="str">
-        <x:v>Inheritance (non-lineage)</x:v>
+      <x:c r="Q5" t="inlineStr">
+        <x:is>
+          <x:t>Inheritance (non-lineage)</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R5" t="str">
-        <x:v>2.00</x:v>
+      <x:c r="R5" t="inlineStr">
+        <x:is>
+          <x:t>2.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>25</x:v>
+      <x:c r="A6" t="inlineStr">
+        <x:is>
+          <x:t>25</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B6" t="str">
-        <x:v>ITL., Art.35.3</x:v>
+      <x:c r="B6" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.3</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D6" t="str">
-        <x:v>Allowances for students</x:v>
+      <x:c r="D6" t="inlineStr">
+        <x:is>
+          <x:t>Allowances for students</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E6" t="str">
-        <x:v>Social</x:v>
+      <x:c r="E6" t="inlineStr">
+        <x:is>
+          <x:t>Social</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F6" t="str">
-        <x:v>Amount #25 Student Allowance LAK</x:v>
+      <x:c r="F6" t="inlineStr">
+        <x:is>
+          <x:t>Amount #25 Student Allowance LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G6" t="str">
-        <x:v>User TE #25</x:v>
+      <x:c r="G6" t="inlineStr">
+        <x:is>
+          <x:t>User TE #25</x:t>
+        </x:is>
       </x:c>
       <x:c r="I6" t="n">
         <x:v>2020</x:v>
@@ -38395,14 +38899,20 @@
       <x:c r="J6" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="K6" t="str">
-        <x:v>25000001.00</x:v>
+      <x:c r="K6" t="inlineStr">
+        <x:is>
+          <x:t>25000001.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L6" t="str">
-        <x:v>65000000.00</x:v>
+      <x:c r="L6" t="inlineStr">
+        <x:is>
+          <x:t>65000000.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M6" t="str">
-        <x:v>20.00</x:v>
+      <x:c r="M6" t="inlineStr">
+        <x:is>
+          <x:t>20.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="O6" t="n">
         <x:v>2020</x:v>
@@ -38410,34 +38920,52 @@
       <x:c r="P6" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q6" t="str">
-        <x:v>Intellectual Property</x:v>
+      <x:c r="Q6" t="inlineStr">
+        <x:is>
+          <x:t>Intellectual Property</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R6" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="R6" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>26</x:v>
+      <x:c r="A7" t="inlineStr">
+        <x:is>
+          <x:t>26</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B7" t="str">
-        <x:v>ITL., Art.35.4</x:v>
+      <x:c r="B7" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.4</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C7" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D7" t="str">
-        <x:v>Profits from sale of shares on Lao stock exchange</x:v>
+      <x:c r="D7" t="inlineStr">
+        <x:is>
+          <x:t>Profits from sale of shares on Lao stock exchange</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E7" t="str">
-        <x:v>Financial Sector</x:v>
+      <x:c r="E7" t="inlineStr">
+        <x:is>
+          <x:t>Financial Sector</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F7" t="str">
-        <x:v>Amount #26 Share Sale Profit LAK</x:v>
+      <x:c r="F7" t="inlineStr">
+        <x:is>
+          <x:t>Amount #26 Share Sale Profit LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G7" t="str">
-        <x:v>User TE #26</x:v>
+      <x:c r="G7" t="inlineStr">
+        <x:is>
+          <x:t>User TE #26</x:t>
+        </x:is>
       </x:c>
       <x:c r="I7" t="n">
         <x:v>2020</x:v>
@@ -38445,12 +38973,16 @@
       <x:c r="J7" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="K7" t="str">
-        <x:v>65000001.00</x:v>
+      <x:c r="K7" t="inlineStr">
+        <x:is>
+          <x:t>65000001.00</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L7" t="str"/>
-      <x:c r="M7" t="str">
-        <x:v>25.00</x:v>
+      <x:c r="L7"/>
+      <x:c r="M7" t="inlineStr">
+        <x:is>
+          <x:t>25.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="O7" t="n">
         <x:v>2020</x:v>
@@ -38458,34 +38990,52 @@
       <x:c r="P7" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q7" t="str">
-        <x:v>Loan Interest (non-bank)</x:v>
+      <x:c r="Q7" t="inlineStr">
+        <x:is>
+          <x:t>Loan Interest (non-bank)</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R7" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="R7" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>27</x:v>
+      <x:c r="A8" t="inlineStr">
+        <x:is>
+          <x:t>27</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B8" t="str">
-        <x:v>ITL., Art.35.4</x:v>
+      <x:c r="B8" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.4</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C8" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D8" t="str">
-        <x:v>Dividends from stock exchange registered companies</x:v>
+      <x:c r="D8" t="inlineStr">
+        <x:is>
+          <x:t>Dividends from stock exchange registered companies</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E8" t="str">
-        <x:v>Financial Sector</x:v>
+      <x:c r="E8" t="inlineStr">
+        <x:is>
+          <x:t>Financial Sector</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F8" t="str">
-        <x:v>Amount #27 Dividend Income LAK</x:v>
+      <x:c r="F8" t="inlineStr">
+        <x:is>
+          <x:t>Amount #27 Dividend Income LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G8" t="str">
-        <x:v>User TE #27</x:v>
+      <x:c r="G8" t="inlineStr">
+        <x:is>
+          <x:t>User TE #27</x:t>
+        </x:is>
       </x:c>
       <x:c r="O8" t="n">
         <x:v>2020</x:v>
@@ -38493,34 +39043,52 @@
       <x:c r="P8" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q8" t="str">
-        <x:v>Lottery Winnings</x:v>
+      <x:c r="Q8" t="inlineStr">
+        <x:is>
+          <x:t>Lottery Winnings</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R8" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="R8" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>28</x:v>
+      <x:c r="A9" t="inlineStr">
+        <x:is>
+          <x:t>28</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B9" t="str">
-        <x:v>ITL., Art.35.11</x:v>
+      <x:c r="B9" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.11</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D9" t="str">
-        <x:v>Interest on bank deposits and government bonds</x:v>
+      <x:c r="D9" t="inlineStr">
+        <x:is>
+          <x:t>Interest on bank deposits and government bonds</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E9" t="str">
-        <x:v>Encourage Savings</x:v>
+      <x:c r="E9" t="inlineStr">
+        <x:is>
+          <x:t>Encourage Savings</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F9" t="str">
-        <x:v>Amount #28.1 / #28.2 Interest LAK</x:v>
+      <x:c r="F9" t="inlineStr">
+        <x:is>
+          <x:t>Amount #28.1 / #28.2 Interest LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G9" t="str">
-        <x:v>User TE #28.1 / #28.2</x:v>
+      <x:c r="G9" t="inlineStr">
+        <x:is>
+          <x:t>User TE #28.1 / #28.2</x:t>
+        </x:is>
       </x:c>
       <x:c r="O9" t="n">
         <x:v>2020</x:v>
@@ -38528,34 +39096,52 @@
       <x:c r="P9" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q9" t="str">
-        <x:v>Online Sales</x:v>
+      <x:c r="Q9" t="inlineStr">
+        <x:is>
+          <x:t>Online Sales</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R9" t="str">
-        <x:v>2.00</x:v>
+      <x:c r="R9" t="inlineStr">
+        <x:is>
+          <x:t>2.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>29</x:v>
+      <x:c r="A10" t="inlineStr">
+        <x:is>
+          <x:t>29</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B10" t="str">
-        <x:v>ITL., Art.35.13</x:v>
+      <x:c r="B10" t="inlineStr">
+        <x:is>
+          <x:t>ITL., Art.35.13</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C10" t="str">
-        <x:v>Exemption</x:v>
+      <x:c r="C10" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D10" t="str">
-        <x:v>Performance bonus for security monitoring/preventing illegal acts</x:v>
+      <x:c r="D10" t="inlineStr">
+        <x:is>
+          <x:t>Performance bonus for security monitoring/preventing illegal acts</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E10" t="str">
-        <x:v>National Security</x:v>
+      <x:c r="E10" t="inlineStr">
+        <x:is>
+          <x:t>National Security</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F10" t="str">
-        <x:v>Amount #29 Security Bonus LAK</x:v>
+      <x:c r="F10" t="inlineStr">
+        <x:is>
+          <x:t>Amount #29 Security Bonus LAK</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G10" t="str">
-        <x:v>User TE #29</x:v>
+      <x:c r="G10" t="inlineStr">
+        <x:is>
+          <x:t>User TE #29</x:t>
+        </x:is>
       </x:c>
       <x:c r="O10" t="n">
         <x:v>2020</x:v>
@@ -38563,34 +39149,52 @@
       <x:c r="P10" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q10" t="str">
-        <x:v>Real Estate Rights Transfer</x:v>
+      <x:c r="Q10" t="inlineStr">
+        <x:is>
+          <x:t>Real Estate Rights Transfer</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R10" t="str">
-        <x:v>2.00</x:v>
+      <x:c r="R10" t="inlineStr">
+        <x:is>
+          <x:t>2.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>30</x:v>
+      <x:c r="A11" t="inlineStr">
+        <x:is>
+          <x:t>30</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B11" t="str">
-        <x:v>Notice 0824/LSO</x:v>
+      <x:c r="B11" t="inlineStr">
+        <x:is>
+          <x:t>Notice 0824/LSO</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C11" t="str">
-        <x:v>Deduction</x:v>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D11" t="str">
-        <x:v>Social security contributions (5.5%, max base 4.5M/mo)</x:v>
+      <x:c r="D11" t="inlineStr">
+        <x:is>
+          <x:t>Social security contributions (5.5%, max base 4.5M/mo)</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E11" t="str">
-        <x:v>Encourage Savings</x:v>
+      <x:c r="E11" t="inlineStr">
+        <x:is>
+          <x:t>Encourage Savings</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F11" t="str">
-        <x:v>Social Security Contribution LAK #30</x:v>
+      <x:c r="F11" t="inlineStr">
+        <x:is>
+          <x:t>Social Security Contribution LAK #30</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G11" t="str">
-        <x:v>User TE #30</x:v>
+      <x:c r="G11" t="inlineStr">
+        <x:is>
+          <x:t>User TE #30</x:t>
+        </x:is>
       </x:c>
       <x:c r="O11" t="n">
         <x:v>2020</x:v>
@@ -38598,11 +39202,15 @@
       <x:c r="P11" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q11" t="str">
-        <x:v>Rental Income</x:v>
+      <x:c r="Q11" t="inlineStr">
+        <x:is>
+          <x:t>Rental Income</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R11" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="R11" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -38612,11 +39220,15 @@
       <x:c r="P12" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="Q12" t="str">
-        <x:v>Shares Transfer</x:v>
+      <x:c r="Q12" t="inlineStr">
+        <x:is>
+          <x:t>Shares Transfer</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R12" t="str">
-        <x:v>2.00</x:v>
+      <x:c r="R12" t="inlineStr">
+        <x:is>
+          <x:t>2.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -38636,31 +39248,47 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="31" t="str">
-        <x:v>Version</x:v>
+      <x:c r="A1" s="31" t="inlineStr">
+        <x:is>
+          <x:t>Version</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B1" s="31" t="str">
-        <x:v>Date</x:v>
+      <x:c r="B1" s="31" t="inlineStr">
+        <x:is>
+          <x:t>Date</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C1" s="31" t="str">
-        <x:v>Owner</x:v>
+      <x:c r="C1" s="31" t="inlineStr">
+        <x:is>
+          <x:t>Owner</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D1" s="31" t="str">
-        <x:v>Change</x:v>
+      <x:c r="D1" s="31" t="inlineStr">
+        <x:is>
+          <x:t>Change</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="28" t="str">
-        <x:v>1.0</x:v>
+      <x:c r="A2" s="28" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B2" s="28" t="str">
-        <x:v>2026-06-05</x:v>
+      <x:c r="B2" s="28" t="inlineStr">
+        <x:is>
+          <x:t>2026-06-05</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C2" s="28" t="str">
-        <x:v>APIS / Tax-ETS</x:v>
+      <x:c r="C2" s="28" t="inlineStr">
+        <x:is>
+          <x:t>APIS / Tax-ETS</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D2" s="28" t="str">
-        <x:v>Initial recommended PIT template with primary provision amounts and user fallback TE fields.</x:v>
+      <x:c r="D2" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Initial recommended PIT template with primary provision amounts and user fallback TE fields.</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
